--- a/data/nzd0133/nzd0133.xlsx
+++ b/data/nzd0133/nzd0133.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I546"/>
+  <dimension ref="A1:I547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18320,6 +18320,39 @@
         <v>380.68</v>
       </c>
       <c r="I546" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>382.58</v>
+      </c>
+      <c r="C547" t="n">
+        <v>407.53</v>
+      </c>
+      <c r="D547" t="n">
+        <v>366.86</v>
+      </c>
+      <c r="E547" t="n">
+        <v>365.83</v>
+      </c>
+      <c r="F547" t="n">
+        <v>355.03</v>
+      </c>
+      <c r="G547" t="n">
+        <v>361.74</v>
+      </c>
+      <c r="H547" t="n">
+        <v>381.1</v>
+      </c>
+      <c r="I547" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18336,7 +18369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B575"/>
+  <dimension ref="A1:B576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24089,6 +24122,16 @@
       </c>
       <c r="B575" t="n">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -24257,28 +24300,28 @@
         <v>0.0101</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.258481394970478</v>
+        <v>-4.271010749898497</v>
       </c>
       <c r="J2" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K2" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3281555946853565</v>
+        <v>0.3301632144618909</v>
       </c>
       <c r="M2" t="n">
-        <v>36.0777730070667</v>
+        <v>36.05784999312404</v>
       </c>
       <c r="N2" t="n">
-        <v>1983.541700420644</v>
+        <v>1981.736982380997</v>
       </c>
       <c r="O2" t="n">
-        <v>44.53697004086205</v>
+        <v>44.51670453190573</v>
       </c>
       <c r="P2" t="n">
-        <v>529.2703390045425</v>
+        <v>529.4090140502126</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24335,28 +24378,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.932079714550936</v>
+        <v>-4.932135549436262</v>
       </c>
       <c r="J3" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K3" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4099634257797244</v>
+        <v>0.4109957470463667</v>
       </c>
       <c r="M3" t="n">
-        <v>34.36710311984097</v>
+        <v>34.3005790989712</v>
       </c>
       <c r="N3" t="n">
-        <v>1843.927576255923</v>
+        <v>1840.347173061302</v>
       </c>
       <c r="O3" t="n">
-        <v>42.9409778213762</v>
+        <v>42.89926774504784</v>
       </c>
       <c r="P3" t="n">
-        <v>540.1139647063178</v>
+        <v>540.1145905589685</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24413,28 +24456,28 @@
         <v>0.0152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7961999602303821</v>
+        <v>-0.8047130341562047</v>
       </c>
       <c r="J4" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K4" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05762868861979487</v>
+        <v>0.05893721192386636</v>
       </c>
       <c r="M4" t="n">
-        <v>18.71779515549152</v>
+        <v>18.71800333223505</v>
       </c>
       <c r="N4" t="n">
-        <v>559.2054959148768</v>
+        <v>559.100784430516</v>
       </c>
       <c r="O4" t="n">
-        <v>23.64752621131599</v>
+        <v>23.6453121026244</v>
       </c>
       <c r="P4" t="n">
-        <v>410.7259077910853</v>
+        <v>410.8184537267668</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24491,28 +24534,28 @@
         <v>0.0286</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5486969191332182</v>
+        <v>-0.5512016773417248</v>
       </c>
       <c r="J5" t="n">
+        <v>546</v>
+      </c>
+      <c r="K5" t="n">
         <v>545</v>
       </c>
-      <c r="K5" t="n">
-        <v>544</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.07801779694871225</v>
+        <v>0.07894905488559656</v>
       </c>
       <c r="M5" t="n">
-        <v>11.26155804097381</v>
+        <v>11.25307396187052</v>
       </c>
       <c r="N5" t="n">
-        <v>195.7261330267003</v>
+        <v>195.4494131783164</v>
       </c>
       <c r="O5" t="n">
-        <v>13.99021561759147</v>
+        <v>13.980322356023</v>
       </c>
       <c r="P5" t="n">
-        <v>387.2868386753579</v>
+        <v>387.3137163217615</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24569,28 +24612,28 @@
         <v>0.0496</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.435549500180854</v>
+        <v>-0.4393035525794829</v>
       </c>
       <c r="J6" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K6" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07734023416667335</v>
+        <v>0.07876948260241312</v>
       </c>
       <c r="M6" t="n">
-        <v>9.125923135779477</v>
+        <v>9.123352000610764</v>
       </c>
       <c r="N6" t="n">
-        <v>124.7063343975748</v>
+        <v>124.6626292973134</v>
       </c>
       <c r="O6" t="n">
-        <v>11.16719903993722</v>
+        <v>11.16524201696109</v>
       </c>
       <c r="P6" t="n">
-        <v>376.7982040337587</v>
+        <v>376.8384656708847</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24647,28 +24690,28 @@
         <v>0.0639</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1064182035221655</v>
+        <v>-0.1100653116492996</v>
       </c>
       <c r="J7" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K7" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005959778077093358</v>
+        <v>0.006388496382837672</v>
       </c>
       <c r="M7" t="n">
-        <v>8.64340733172576</v>
+        <v>8.643153254268755</v>
       </c>
       <c r="N7" t="n">
-        <v>104.083788118787</v>
+        <v>104.0675717843023</v>
       </c>
       <c r="O7" t="n">
-        <v>10.20214625060761</v>
+        <v>10.20135146852133</v>
       </c>
       <c r="P7" t="n">
-        <v>374.3823162671782</v>
+        <v>374.4214309433686</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24725,28 +24768,28 @@
         <v>0.0476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03140656690180803</v>
+        <v>0.0292930598306601</v>
       </c>
       <c r="J8" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K8" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001902247881243824</v>
+        <v>0.001658767962726237</v>
       </c>
       <c r="M8" t="n">
-        <v>3.888017500834233</v>
+        <v>3.891763139294667</v>
       </c>
       <c r="N8" t="n">
-        <v>28.5287689904919</v>
+        <v>28.53462216704379</v>
       </c>
       <c r="O8" t="n">
-        <v>5.341232909215989</v>
+        <v>5.341780804848116</v>
       </c>
       <c r="P8" t="n">
-        <v>385.9060815215014</v>
+        <v>385.928798335428</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24784,7 +24827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I546"/>
+  <dimension ref="A1:I547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50173,6 +50216,53 @@
         </is>
       </c>
     </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-36.543349696425885,174.71001415409367</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-36.54410368071902,174.71007919816256</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-36.54472622750472,174.7094189710042</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-36.54538916238982,174.70904787282862</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-36.54600783182165,174.7085626747726</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-36.54669777751911,174.70831424839994</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>-36.547425957095406,174.7084529317294</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0133/nzd0133.xlsx
+++ b/data/nzd0133/nzd0133.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I547"/>
+  <dimension ref="A1:I548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18353,6 +18353,39 @@
         <v>381.1</v>
       </c>
       <c r="I547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>389.86</v>
+      </c>
+      <c r="C548" t="n">
+        <v>415.5</v>
+      </c>
+      <c r="D548" t="n">
+        <v>370.57</v>
+      </c>
+      <c r="E548" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="F548" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="G548" t="n">
+        <v>362.24</v>
+      </c>
+      <c r="H548" t="n">
+        <v>383.95</v>
+      </c>
+      <c r="I548" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18369,7 +18402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B576"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24132,6 +24165,16 @@
       </c>
       <c r="B576" t="n">
         <v>0.75</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -24300,28 +24343,28 @@
         <v>0.0101</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.271010749898497</v>
+        <v>-4.280421663307844</v>
       </c>
       <c r="J2" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K2" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3301632144618909</v>
+        <v>0.3319772359757308</v>
       </c>
       <c r="M2" t="n">
-        <v>36.05784999312404</v>
+        <v>36.02506547830254</v>
       </c>
       <c r="N2" t="n">
-        <v>1981.736982380997</v>
+        <v>1979.047727453415</v>
       </c>
       <c r="O2" t="n">
-        <v>44.51670453190573</v>
+        <v>44.48648926869162</v>
       </c>
       <c r="P2" t="n">
-        <v>529.4090140502126</v>
+        <v>529.514014367986</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24378,28 +24421,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.932135549436262</v>
+        <v>-4.92861828006891</v>
       </c>
       <c r="J3" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K3" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4109957470463667</v>
+        <v>0.4116880294617673</v>
       </c>
       <c r="M3" t="n">
-        <v>34.3005790989712</v>
+        <v>34.25525068934549</v>
       </c>
       <c r="N3" t="n">
-        <v>1840.347173061302</v>
+        <v>1836.930184030067</v>
       </c>
       <c r="O3" t="n">
-        <v>42.89926774504784</v>
+        <v>42.85942351490588</v>
       </c>
       <c r="P3" t="n">
-        <v>540.1145905589685</v>
+        <v>540.0748484514581</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24456,28 +24499,28 @@
         <v>0.0152</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8047130341562047</v>
+        <v>-0.8117904290027377</v>
       </c>
       <c r="J4" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K4" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05893721192386636</v>
+        <v>0.06009821282966288</v>
       </c>
       <c r="M4" t="n">
-        <v>18.71800333223505</v>
+        <v>18.71198365364438</v>
       </c>
       <c r="N4" t="n">
-        <v>559.100784430516</v>
+        <v>558.6965117950649</v>
       </c>
       <c r="O4" t="n">
-        <v>23.6453121026244</v>
+        <v>23.63676187203029</v>
       </c>
       <c r="P4" t="n">
-        <v>410.8184537267668</v>
+        <v>410.8960001384204</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24534,28 +24577,28 @@
         <v>0.0286</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5512016773417248</v>
+        <v>-0.5527223787319411</v>
       </c>
       <c r="J5" t="n">
+        <v>547</v>
+      </c>
+      <c r="K5" t="n">
         <v>546</v>
       </c>
-      <c r="K5" t="n">
-        <v>545</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.07894905488559656</v>
+        <v>0.07965465001100591</v>
       </c>
       <c r="M5" t="n">
-        <v>11.25307396187052</v>
+        <v>11.2397173100361</v>
       </c>
       <c r="N5" t="n">
-        <v>195.4494131783164</v>
+        <v>195.1210723722451</v>
       </c>
       <c r="O5" t="n">
-        <v>13.980322356023</v>
+        <v>13.96857445741136</v>
       </c>
       <c r="P5" t="n">
-        <v>387.3137163217615</v>
+        <v>387.3301657209157</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24612,28 +24655,28 @@
         <v>0.0496</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4393035525794829</v>
+        <v>-0.443011515341997</v>
       </c>
       <c r="J6" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K6" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07876948260241312</v>
+        <v>0.08021061905910354</v>
       </c>
       <c r="M6" t="n">
-        <v>9.123352000610764</v>
+        <v>9.120407677527094</v>
       </c>
       <c r="N6" t="n">
-        <v>124.6626292973134</v>
+        <v>124.61041671297</v>
       </c>
       <c r="O6" t="n">
-        <v>11.16524201696109</v>
+        <v>11.16290359686806</v>
       </c>
       <c r="P6" t="n">
-        <v>376.8384656708847</v>
+        <v>376.8785539467738</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24690,28 +24733,28 @@
         <v>0.0639</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1100653116492996</v>
+        <v>-0.1135336921040184</v>
       </c>
       <c r="J7" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K7" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006388496382837672</v>
+        <v>0.006813730380157423</v>
       </c>
       <c r="M7" t="n">
-        <v>8.643153254268755</v>
+        <v>8.641832379401901</v>
       </c>
       <c r="N7" t="n">
-        <v>104.0675717843023</v>
+        <v>104.0310735179105</v>
       </c>
       <c r="O7" t="n">
-        <v>10.20135146852133</v>
+        <v>10.19956241796238</v>
       </c>
       <c r="P7" t="n">
-        <v>374.4214309433686</v>
+        <v>374.4589289986249</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24768,28 +24811,28 @@
         <v>0.0476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0292930598306601</v>
+        <v>0.02824491632569867</v>
       </c>
       <c r="J8" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K8" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001658767962726237</v>
+        <v>0.001548247657947033</v>
       </c>
       <c r="M8" t="n">
-        <v>3.891763139294667</v>
+        <v>3.889909544514633</v>
       </c>
       <c r="N8" t="n">
-        <v>28.53462216704379</v>
+        <v>28.49587780838178</v>
       </c>
       <c r="O8" t="n">
-        <v>5.341780804848116</v>
+        <v>5.338153033435983</v>
       </c>
       <c r="P8" t="n">
-        <v>385.928798335428</v>
+        <v>385.9401556861976</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24827,7 +24870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I547"/>
+  <dimension ref="A1:I548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50263,6 +50306,53 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-36.54336400231399,174.7100935101685</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-36.54411977094868,174.71016595613585</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-36.54473660983046,174.7094583615295</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-36.54539824726255,174.70907391374652</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-36.54600813583233,174.7085636067654</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-36.54669872540359,174.7083197083382</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>-36.54742783796223,174.70848468044653</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
